--- a/artfynd/A 50673-2025 artfynd.xlsx
+++ b/artfynd/A 50673-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>129001080</v>
       </c>
       <c r="B3" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50673-2025 artfynd.xlsx
+++ b/artfynd/A 50673-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>129001080</v>
       </c>
       <c r="B3" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50673-2025 artfynd.xlsx
+++ b/artfynd/A 50673-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>129001080</v>
       </c>
       <c r="B3" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50673-2025 artfynd.xlsx
+++ b/artfynd/A 50673-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>129001080</v>
       </c>
       <c r="B3" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50673-2025 artfynd.xlsx
+++ b/artfynd/A 50673-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>129001080</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50673-2025 artfynd.xlsx
+++ b/artfynd/A 50673-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>129001080</v>
       </c>
       <c r="B3" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50673-2025 artfynd.xlsx
+++ b/artfynd/A 50673-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>129001080</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
